--- a/data/trans_dic/IP1012-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1012-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen ceguera o problemas de visión</t>
+          <t>Menores que padecen ceguera o problemas de visión (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -797,17 +798,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,35</t>
+          <t>0,26; 2,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -817,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,2</t>
+          <t>0,13; 1,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,6</t>
+          <t>0,13; 1,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -897,42 +898,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,96</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,98</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,7</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,19</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1007,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1022,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,0</t>
+          <t>0,31; 3,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,87</t>
+          <t>0,35; 2,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,12</t>
+          <t>0,34; 2,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,3</t>
+          <t>0,37; 2,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,83</t>
+          <t>0,09; 0,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1132,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,5</t>
+          <t>0,36; 1,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,58</t>
+          <t>0,36; 1,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,1; 0,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,93</t>
+          <t>0,29; 1,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,12</t>
+          <t>0,35; 1,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,46</t>
+          <t>0,05; 0,47</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen ceguera o problemas de visión (tasa de respuesta: 99,78%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1459</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1459</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4858</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5091</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2656</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3294</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3309</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>648; 5425</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 7130</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3258</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>674; 6707</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>654; 8188</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3252</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4588</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4217</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3193</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3052</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4682</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6404</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3107</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1672</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2374</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3749</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3602</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4854</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5852</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 0</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>640; 7074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>614; 5266</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5092</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1378; 9436</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1298; 8013</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4470</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3243</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7698</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9315</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>629; 5321</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>918; 7671</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2599; 10758</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2687; 11670</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>709; 6374</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4093; 14199</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5055; 16405</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>714; 6846</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1012-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1012-Edad-trans_dic.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,14</t>
+          <t>0,25; 2,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,32</t>
+          <t>0,13; 1,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,63</t>
+          <t>0,13; 1,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,32 +913,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,43</t>
+          <t>0,31; 3,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,96</t>
+          <t>0,35; 3,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,36</t>
+          <t>0,34; 2,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,29</t>
+          <t>0,38; 2,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,78</t>
+          <t>0,09; 0,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,09</t>
+          <t>0,13; 1,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,49</t>
+          <t>0,36; 1,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,56</t>
+          <t>0,37; 1,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,86</t>
+          <t>0,1; 0,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,01</t>
+          <t>0,28; 0,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,13</t>
+          <t>0,34; 1,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,47</t>
+          <t>0,05; 0,48</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4858</t>
+          <t>0; 4546</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5091</t>
+          <t>0; 4560</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3294</t>
+          <t>0; 3187</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3309</t>
+          <t>0; 3316</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>648; 5425</t>
+          <t>644; 5365</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3258</t>
+          <t>0; 3638</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>674; 6707</t>
+          <t>652; 7061</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>654; 8188</t>
+          <t>654; 6835</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3252</t>
+          <t>0; 3219</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4588</t>
+          <t>0; 4575</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1758,32 +1758,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4217</t>
+          <t>0; 4483</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3193</t>
+          <t>0; 2950</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3052</t>
+          <t>0; 3459</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4682</t>
+          <t>0; 4553</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 6404</t>
+          <t>0; 4891</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3107</t>
+          <t>0; 3117</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4854</t>
+          <t>0; 4661</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5852</t>
+          <t>0; 6448</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,32 +1921,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>640; 7074</t>
+          <t>643; 6911</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>614; 5266</t>
+          <t>618; 5814</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5092</t>
+          <t>0; 5223</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1378; 9436</t>
+          <t>1361; 8440</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1298; 8013</t>
+          <t>1316; 8039</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4470</t>
+          <t>0; 5577</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>629; 5321</t>
+          <t>635; 5399</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>918; 7671</t>
+          <t>922; 8247</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2084,32 +2084,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2599; 10758</t>
+          <t>2617; 10956</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2687; 11670</t>
+          <t>2785; 11252</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>709; 6374</t>
+          <t>723; 6831</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4093; 14199</t>
+          <t>3978; 13576</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5055; 16405</t>
+          <t>5006; 15621</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>714; 6846</t>
+          <t>710; 6957</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1012-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1012-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,22 +630,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -683,24 +683,24 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,31</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,13</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,42 +788,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,26; 2,35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,33</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,42</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>0,0; 1,41</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,25; 2,11</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,67</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,41</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,39</t>
+          <t>0,13; 1,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,36</t>
+          <t>0,13; 1,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,19</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,66</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,95</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,98</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,17</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,86</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,83</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,37 +1008,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,31; 3,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,35; 2,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,56</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,51</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,5</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,31; 3,35</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,35; 3,27</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,0</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,11</t>
+          <t>0,34; 2,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,79</t>
+          <t>0,35; 1,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,17</t>
+          <t>0,36; 1,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0,1; 0,89</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 0,83</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,13; 1,09</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,36; 1,52</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 1,5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,92</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,97</t>
+          <t>0,28; 0,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,07</t>
+          <t>0,35; 1,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,48</t>
+          <t>0,05; 0,46</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,22 +1316,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>1459</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1459</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1422,24 +1422,24 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 4816</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4546</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4560</t>
+          <t>0; 5180</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3187</t>
+          <t>649; 5958</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3316</t>
+          <t>0; 6211</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0; 3256</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3604</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3313</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>644; 5365</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 7130</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3638</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>652; 7061</t>
+          <t>674; 6076</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>654; 6835</t>
+          <t>654; 8001</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 3250</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>915</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 4517</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3337</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3125</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4575</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4608</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4483</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2950</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3459</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4553</t>
+          <t>0; 3908</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4891</t>
+          <t>0; 5569</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3117</t>
+          <t>0; 3092</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2374</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1375</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1672</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2374</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4661</t>
+          <t>638; 6185</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6448</t>
+          <t>617; 5108</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>0; 4450</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4867</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5998</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>0; 0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>643; 6911</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>618; 5814</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0; 5223</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1361; 8440</t>
+          <t>1380; 8498</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1316; 8039</t>
+          <t>1311; 8044</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5577</t>
+          <t>0; 5225</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>3243</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>635; 5399</t>
+          <t>2498; 10822</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>922; 8247</t>
+          <t>2721; 11838</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>711; 6647</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>634; 5643</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>923; 7739</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>0; 0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2617; 10956</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2785; 11252</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>723; 6831</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3978; 13576</t>
+          <t>3940; 13064</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5006; 15621</t>
+          <t>5134; 16326</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>710; 6957</t>
+          <t>712; 6690</t>
         </is>
       </c>
     </row>
